--- a/survey_templates/039_salon_rebooking_behavior_survey--survey_templates.xlsx
+++ b/survey_templates/039_salon_rebooking_behavior_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>client_loyalty</t>
+          <t>rebooking_frequency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>client_loyalty</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your rebooking frequency?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select your rebooking frequency</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rebooking_habits</t>
+          <t>service_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rebooking_habits</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What type of service do you usually rebook?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select the type of service you usually rebook</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,43 +569,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rebooking_frequency</t>
+          <t>rebooking_window</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rebooking_frequency</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How often do you rebook your appointments?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select the rebooking window</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>service_type</t>
+          <t>appointment_satisfaction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>service_type</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How would you rate your satisfaction with your last appointment?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please rate your satisfaction</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>booking_window</t>
+          <t>rebooking_habits</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>booking_window</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Rebooking Habits</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select your rebooking habits</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>client_satisfaction</t>
+          <t>rebooking_reason</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>client_satisfaction</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Why do you rebook your appointments?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide a note about your rebooking reasons</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is your preferred contact method for rebooking?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select your preferred contact method</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>appointment_rebooking_window</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How long before your next appointment will be rebooked?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please select the rebooking window</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>rebooking_window_unit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_info_email</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What unit do you use to measure your rebooking window?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select the unit you use</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_info_phone</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Do you have any additional comments about your rebooking behavior?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>client_satisfaction_comment</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>client_satisfaction_comment</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your phone number?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please enter your phone number</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,320 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>appointment_satisfaction</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>appointment_satisfaction</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Is there anything else you'd like to comment about your rebooking behavior?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>appointment_rebooking</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>appointment_rebooking</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>appointment_satisfaction</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>appointment_satisfaction</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rebooking_window</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>rebooking_window</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>rebooking_window_range</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rebooking_window_range</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>rebooking_window_unit</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>rebooking_window_unit</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>rebooking_window_reason</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>rebooking_window_reason</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_reason</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_reason</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window_unit</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window_unit</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window_reason</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window_reason</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,782 +875,425 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>client_loyalty_choices</t>
+          <t>rebooking_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>always_rebook</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Always rebook</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>client_loyalty_choices</t>
+          <t>rebooking_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>rarely_rebook</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rarely rebook</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>client_loyalty_choices</t>
+          <t>rebooking_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>never_rebook</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Never rebook</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rebooking_habits_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'always_rebook'}</t>
+          <t>hair_cut</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Always rebook'}</t>
+          <t>Hair cut</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rebooking_habits_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_rebook'}</t>
+          <t>color_treatment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely rebook'}</t>
+          <t>Color treatment</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rebooking_habits_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'never_rebook'}</t>
+          <t>chemical_service</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Never rebook'}</t>
+          <t>Chemical service</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>rebooking_window_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'hair_cut'}</t>
+          <t>1-2_weeks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Hair cut'}</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>rebooking_window_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'color_treatment'}</t>
+          <t>2-4_weeks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Color treatment'}</t>
+          <t>2-4 weeks</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>rebooking_window_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'chemical_service'}</t>
+          <t>4-6_weeks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Chemical service'}</t>
+          <t>4-6 weeks</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>client_satisfaction_choices</t>
+          <t>appointment_satisfaction_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>client_satisfaction_choices</t>
+          <t>appointment_satisfaction_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>client_satisfaction_choices</t>
+          <t>appointment_satisfaction_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>client_satisfaction_choices</t>
+          <t>appointment_satisfaction_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>client_satisfaction_choices</t>
+          <t>appointment_satisfaction_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>rebooking_habits_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>rebooking_habits_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>appointment_satisfaction_choices</t>
+          <t>rebooking_habits_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>appointment_satisfaction_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>appointment_satisfaction_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>appointment_satisfaction_choices</t>
+          <t>appointment_rebooking_window_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>1-2_weeks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>appointment_satisfaction_choices</t>
+          <t>appointment_rebooking_window_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>2-4_weeks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>2-4 weeks</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>appointment_rebooking_choices</t>
+          <t>appointment_rebooking_window_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'always_rebook'}</t>
+          <t>4-6_weeks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Always rebook'}</t>
+          <t>4-6 weeks</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>appointment_rebooking_choices</t>
+          <t>rebooking_window_unit_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_rebook'}</t>
+          <t>days</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely rebook'}</t>
+          <t>days</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>appointment_rebooking_choices</t>
+          <t>rebooking_window_unit_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'never_rebook'}</t>
+          <t>weeks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Never rebook'}</t>
+          <t>weeks</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>appointment_satisfaction_choices</t>
+          <t>rebooking_window_unit_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>appointment_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>appointment_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'label':_'neutral'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'label': 'Neutral'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>appointment_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>appointment_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'label':_'very_dissatisfied'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'label': 'Very dissatisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>rebooking_window_range_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1-2_weeks</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1-2 weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>rebooking_window_range_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2-4_weeks</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2-4 weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>rebooking_window_range_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4-6_weeks</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>4-6 weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>rebooking_window_unit_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>rebooking_window_unit_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>weeks</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>rebooking_window_unit_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
           <t>months</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_reason_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>always_rebook</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Always rebook</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_reason_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>rarely_rebook</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Rarely rebook</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_reason_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>never_rebook</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Never rebook</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1-2_weeks</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1-2 weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2-4_weeks</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2-4 weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>4-6_weeks</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>4-6 weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window_unit_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window_unit_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>weeks</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>appointment_rebooking_window_unit_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>email</t>
         </is>
       </c>
     </row>
